--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104659_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104659_W23.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4055</v>
+        <v>3.2793</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4954</v>
+        <v>3.3463</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.067</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1374</v>
+        <v>2.1318</v>
       </c>
       <c r="H2" t="n">
-        <v>3.081</v>
+        <v>3.0654</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9435</v>
+        <v>-0.9335</v>
       </c>
       <c r="J2" t="n">
-        <v>3.355</v>
+        <v>3.3327</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3177</v>
+        <v>3.2955</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2176</v>
+        <v>-1.2009</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6291</v>
+        <v>0.5133</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0212</v>
+        <v>-0.0955</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6079</v>
+        <v>0.6088</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5013</v>
+        <v>0.0462</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4333</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.5329</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.446</v>
+        <v>-2.4552</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2915</v>
+        <v>0.2874</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.7375</v>
+        <v>-2.7426</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0774</v>
+        <v>0.0525</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2051</v>
+        <v>1.1926</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1276</v>
+        <v>-1.1401</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5234</v>
+        <v>-2.5077</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6099</v>
+        <v>-1.6025</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1988</v>
+        <v>0.7502</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0344</v>
+        <v>0.2111</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1644</v>
+        <v>0.5391</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.1212</v>
+        <v>-0.4272</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.721</v>
+        <v>-0.3948</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4002</v>
+        <v>-0.0324</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.5856</v>
+        <v>-2.5909</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1226</v>
+        <v>0.1235</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.7082</v>
+        <v>-2.7144</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.1362</v>
+        <v>-1.1611</v>
       </c>
       <c r="K4" t="n">
-        <v>0.218</v>
+        <v>0.2101</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3542</v>
+        <v>-1.3712</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4494</v>
+        <v>-1.4298</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5356</v>
+        <v>0.1637</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6775</v>
+        <v>-0.3232</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1418</v>
+        <v>0.4868</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RUBIT</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.7821</v>
+        <v>-1.3285</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9466</v>
+        <v>1.0475</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8355</v>
+        <v>-2.3759</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.7635</v>
+        <v>1.279</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.505</v>
+        <v>1.5769</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2585</v>
+        <v>-0.2979</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1864</v>
+        <v>2.3669</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.261</v>
+        <v>1.965</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>0.4019</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5771</v>
+        <v>-1.0879</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.244</v>
+        <v>-0.3881</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3331</v>
+        <v>-0.6998</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.2543</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6261</v>
+        <v>-0.1813</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1657</v>
+        <v>0.4356</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>-2.1789</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>A. RUBIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.786</v>
+        <v>-1.8423</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8304</v>
+        <v>-0.96</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.6164</v>
+        <v>-0.8822</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2816</v>
+        <v>-2.7575</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5801</v>
+        <v>-2.5045</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2985</v>
+        <v>-0.253</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3819</v>
+        <v>-1.1945</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9741</v>
+        <v>-1.269</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4078</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1003</v>
+        <v>-1.5629</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.394</v>
+        <v>-1.2355</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7063</v>
+        <v>-0.3275</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2017</v>
+        <v>-0.8572</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4174</v>
+        <v>-0.6273</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2156</v>
+        <v>-0.2298</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5577</v>
+        <v>-2.0762</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1265</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4313</v>
+        <v>-1.2894</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4295</v>
+        <v>-1.4287</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5628</v>
+        <v>-1.5597</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1333</v>
+        <v>0.131</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2574</v>
+        <v>-0.267</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6651</v>
+        <v>-0.669</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1721</v>
+        <v>-1.1617</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4912</v>
+        <v>-0.0117</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4174</v>
+        <v>-0.0629</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6725</v>
+        <v>-2.4335</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2253</v>
+        <v>-2.1296</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4472</v>
+        <v>-0.3039</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9545</v>
+        <v>-1.9572</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0549</v>
+        <v>1.0487</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.0094</v>
+        <v>-3.0059</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5528</v>
+        <v>-0.5708</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9453</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4017</v>
+        <v>-1.3865</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0375</v>
+        <v>0.2067</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5383</v>
+        <v>-0.4207</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5008</v>
+        <v>0.6273</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0096</v>
+        <v>-3.1643</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4101</v>
+        <v>-2.308</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5995</v>
+        <v>-0.8563</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.0073</v>
+        <v>-4.0016</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3548</v>
+        <v>-2.3605</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6525</v>
+        <v>-1.641</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3667</v>
+        <v>-1.3809</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.4413</v>
+        <v>-1.4554</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6407</v>
+        <v>-2.6207</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5901</v>
+        <v>-0.7561</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0434</v>
+        <v>-0.9271</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4533</v>
+        <v>0.171</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5569</v>
+        <v>-3.5436</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3125</v>
+        <v>-1.1143</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2445</v>
+        <v>-2.4293</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4143</v>
+        <v>-1.4144</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9394</v>
+        <v>0.9392</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3537</v>
+        <v>-2.3536</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9777</v>
+        <v>1.9523</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5456</v>
+        <v>2.5338</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5679</v>
+        <v>-0.5816</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.392</v>
+        <v>-3.3667</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6062</v>
+        <v>-1.5946</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7858</v>
+        <v>-1.772</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5302</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9557</v>
+        <v>-0.7204</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4255</v>
+        <v>0.2058</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9212</v>
+        <v>-3.6211</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7982</v>
+        <v>-2.5797</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.123</v>
+        <v>-1.0414</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.6797</v>
+        <v>-3.6825</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2221</v>
+        <v>-1.2262</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.4576</v>
+        <v>-2.4563</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1903</v>
+        <v>-2.2078</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6549</v>
+        <v>-0.6657</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4894</v>
+        <v>-1.4747</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3756</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6079</v>
+        <v>-0.3719</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2323</v>
+        <v>0.2951</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5979</v>
+        <v>-4.8063</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4365</v>
+        <v>-2.8312</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1614</v>
+        <v>-1.9751</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1322</v>
+        <v>-3.142</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7457</v>
+        <v>-2.7593</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3865</v>
+        <v>-0.3827</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3157</v>
+        <v>0.284</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6518</v>
+        <v>-0.6765</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.4479</v>
+        <v>-3.426</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0939</v>
+        <v>-2.0829</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.8236</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2571</v>
+        <v>-0.6112</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3675</v>
+        <v>-0.2124</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.9244</v>
+        <v>-6.1053</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1115</v>
+        <v>-2.4813</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.8129</v>
+        <v>-3.6239</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6377</v>
+        <v>-3.6277</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9452</v>
+        <v>-1.9417</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6926</v>
+        <v>-1.686</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.574</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.0747</v>
+        <v>-3.0536</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0939</v>
+        <v>-2.0829</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.555</v>
+        <v>-0.7539</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1875</v>
+        <v>-0.5415</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3675</v>
+        <v>-0.2124</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-26.0227</v>
+        <v>-26.0228</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.3291</v>
+        <v>-10.6128</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.6937</v>
+        <v>-15.4097</v>
       </c>
       <c r="G14" t="n">
-        <v>-23.6313</v>
+        <v>-23.6469</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.2661</v>
+        <v>-5.3108</v>
       </c>
       <c r="I14" t="n">
-        <v>-18.3652</v>
+        <v>-18.3359</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8548999999999995</v>
+        <v>0.6323000000000004</v>
       </c>
       <c r="K14" t="n">
-        <v>5.680400000000001</v>
+        <v>5.536499999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.8253</v>
+        <v>-4.904400000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-24.4863</v>
+        <v>-24.2791</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.9464</v>
+        <v>-10.8476</v>
       </c>
       <c r="O14" t="n">
-        <v>-13.5399</v>
+        <v>-13.4317</v>
       </c>
       <c r="P14" t="n">
-        <v>3.402400000000001</v>
+        <v>3.4144</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2076</v>
+        <v>-10.2434</v>
       </c>
       <c r="R14" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9053</v>
+        <v>-1.9057</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.6727</v>
+        <v>-4.671900000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.767099999999999</v>
+        <v>2.7661</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.8884</v>
+        <v>-3.8844</v>
       </c>
       <c r="W14" t="n">
-        <v>3.696</v>
+        <v>3.6703</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.5844</v>
+        <v>-7.5549</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.379300000000001</v>
+        <v>8.238899999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2705</v>
+        <v>6.4837</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1088</v>
+        <v>1.7552</v>
       </c>
       <c r="G15" t="n">
-        <v>7.2385</v>
+        <v>7.2352</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7214</v>
+        <v>0.7291</v>
       </c>
       <c r="I15" t="n">
-        <v>6.5171</v>
+        <v>6.5062</v>
       </c>
       <c r="J15" t="n">
-        <v>6.827</v>
+        <v>6.8044</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1949</v>
+        <v>1.1893</v>
       </c>
       <c r="L15" t="n">
-        <v>5.6321</v>
+        <v>5.6151</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4115</v>
+        <v>0.4308</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O15" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4603</v>
+        <v>0.3207</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5565</v>
+        <v>-0.3207</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0168</v>
+        <v>0.6415</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>P. MILLS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5807</v>
+        <v>5.0242</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2577</v>
+        <v>4.3691</v>
       </c>
       <c r="F16" t="n">
-        <v>2.323</v>
+        <v>0.6552</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4627</v>
+        <v>2.8114</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7617</v>
+        <v>-0.9765</v>
       </c>
       <c r="I16" t="n">
-        <v>0.701</v>
+        <v>3.7879</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3575</v>
+        <v>3.8858</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9524</v>
+        <v>0.6615</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4051</v>
+        <v>3.2243</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1052</v>
+        <v>-1.0744</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1908</v>
+        <v>-1.638</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2959</v>
+        <v>0.5636</v>
       </c>
       <c r="P16" t="n">
-        <v>1.361</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6643</v>
+        <v>-0.0964</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8075</v>
+        <v>-0.4601</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8568</v>
+        <v>0.3637</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>4.3579</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>4.3579</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MILLS</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2506</v>
+        <v>4.6754</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1922</v>
+        <v>2.4152</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0584</v>
+        <v>2.2602</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8176</v>
+        <v>1.4733</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9754</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>3.793</v>
+        <v>0.6985</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9196</v>
+        <v>1.3423</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6785</v>
+        <v>0.948</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2411</v>
+        <v>0.3943</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.102</v>
+        <v>0.131</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6539</v>
+        <v>-0.1733</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.3043</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8961</v>
+        <v>0.7469</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6956</v>
+        <v>-0.0166</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2005</v>
+        <v>0.7634</v>
       </c>
       <c r="V17" t="n">
-        <v>4.3707</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>4.3707</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7341</v>
+        <v>2.863</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0168</v>
+        <v>1.0857</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7173</v>
+        <v>1.7773</v>
       </c>
       <c r="G18" t="n">
-        <v>4.7627</v>
+        <v>4.7466</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9337</v>
+        <v>3.9184</v>
       </c>
       <c r="I18" t="n">
-        <v>0.829</v>
+        <v>0.8282</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8367</v>
+        <v>4.7999</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8718</v>
+        <v>3.8471</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9648</v>
+        <v>0.9528</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.074</v>
+        <v>-0.0533</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3324</v>
+        <v>0.4822</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7497</v>
+        <v>0.782</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6207</v>
+        <v>2.3317</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3049</v>
+        <v>0.0423</v>
       </c>
       <c r="F19" t="n">
-        <v>2.3158</v>
+        <v>2.2894</v>
       </c>
       <c r="G19" t="n">
-        <v>1.934</v>
+        <v>1.9386</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9074</v>
+        <v>1.918</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0266</v>
+        <v>0.0206</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9411</v>
+        <v>0.9194</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9568</v>
+        <v>1.9478</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.0157</v>
+        <v>-1.0284</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9929</v>
+        <v>1.0192</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0494</v>
+        <v>-0.0298</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9155</v>
+        <v>0.6192</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0484</v>
+        <v>-0.2837</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9639</v>
+        <v>0.9028</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5543</v>
+        <v>2.2179</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0155</v>
+        <v>1.5267</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5387</v>
+        <v>0.6911</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4131</v>
+        <v>0.4138</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1414</v>
+        <v>-0.1435</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5545</v>
+        <v>0.5572</v>
       </c>
       <c r="J20" t="n">
-        <v>1.577</v>
+        <v>1.5594</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9453</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6317</v>
+        <v>0.6254</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1639</v>
+        <v>-1.1457</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5553</v>
+        <v>0.2091</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4386</v>
+        <v>-0.0327</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1167</v>
+        <v>0.2418</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9978</v>
+        <v>1.2521</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0574</v>
+        <v>1.1726</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0596</v>
+        <v>0.0795</v>
       </c>
       <c r="G21" t="n">
-        <v>1.128</v>
+        <v>1.1346</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5167</v>
+        <v>-0.5115</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6446</v>
+        <v>1.6461</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2661</v>
+        <v>1.2633</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1381</v>
+        <v>-0.1287</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1963</v>
+        <v>0.0476</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0124</v>
+        <v>0.1383</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8172</v>
+        <v>1.031</v>
       </c>
       <c r="E22" t="n">
-        <v>0.456</v>
+        <v>0.4237</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3613</v>
+        <v>0.6073</v>
       </c>
       <c r="G22" t="n">
-        <v>3.7107</v>
+        <v>3.715</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7584</v>
+        <v>3.7583</v>
       </c>
       <c r="J22" t="n">
-        <v>4.0455</v>
+        <v>4.0289</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4258</v>
+        <v>0.4169</v>
       </c>
       <c r="L22" t="n">
-        <v>3.6197</v>
+        <v>3.612</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3348</v>
+        <v>-0.3139</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2395</v>
+        <v>-0.0207</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1083</v>
+        <v>0.3278</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5747</v>
+        <v>0.8413</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6909</v>
+        <v>-0.3557</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2656</v>
+        <v>1.1971</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8093</v>
+        <v>0.8194</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0735</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7357</v>
+        <v>0.7421</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1173</v>
+        <v>1.1058</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8934</v>
+        <v>0.8823</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.308</v>
+        <v>-0.2863</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1685</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6663</v>
+        <v>0.5729</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5011</v>
+        <v>-0.5639</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9568</v>
+        <v>-0.8488</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4556</v>
+        <v>0.2848</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4144</v>
+        <v>-0.413</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4386</v>
+        <v>0.4421</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.853</v>
+        <v>-0.8551</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7481</v>
+        <v>-0.7581</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6754</v>
+        <v>0.6722</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3337</v>
+        <v>0.3451</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5523</v>
+        <v>0.4833</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7609</v>
+        <v>0.574</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9856</v>
+        <v>-1.099</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.3904</v>
+        <v>-1.0624</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5952</v>
+        <v>-0.0367</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.2308</v>
+        <v>-0.228</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8891</v>
+        <v>-0.8739</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6583</v>
+        <v>0.6459</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6533</v>
+        <v>-0.672</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4224</v>
+        <v>0.444</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2066</v>
+        <v>-0.1877</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0743</v>
+        <v>-0.1881</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3787</v>
+        <v>0.1535</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>26.0227</v>
+        <v>26.8126</v>
       </c>
       <c r="E26" t="n">
-        <v>15.5329</v>
+        <v>15.2521</v>
       </c>
       <c r="F26" t="n">
-        <v>10.4897</v>
+        <v>11.5604</v>
       </c>
       <c r="G26" t="n">
-        <v>23.6314</v>
+        <v>23.6469</v>
       </c>
       <c r="H26" t="n">
-        <v>5.266</v>
+        <v>5.3109</v>
       </c>
       <c r="I26" t="n">
-        <v>18.3652</v>
+        <v>18.3359</v>
       </c>
       <c r="J26" t="n">
-        <v>24.4864</v>
+        <v>24.2791</v>
       </c>
       <c r="K26" t="n">
-        <v>10.9464</v>
+        <v>10.8474</v>
       </c>
       <c r="L26" t="n">
-        <v>13.54</v>
+        <v>13.4316</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8551000000000003</v>
+        <v>-0.6321999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-5.680399999999999</v>
+        <v>-5.536700000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>4.8253</v>
+        <v>4.9045</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.4025</v>
+        <v>-3.414500000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-13.6101</v>
+        <v>-13.6581</v>
       </c>
       <c r="R26" t="n">
-        <v>10.2075</v>
+        <v>10.2435</v>
       </c>
       <c r="S26" t="n">
-        <v>1.9054</v>
+        <v>2.6956</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.7673</v>
+        <v>-2.7663</v>
       </c>
       <c r="U26" t="n">
-        <v>4.6726</v>
+        <v>5.4617</v>
       </c>
       <c r="V26" t="n">
-        <v>3.888600000000001</v>
+        <v>3.884599999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>7.4238</v>
+        <v>7.3972</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.5352</v>
+        <v>-3.5125</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104659_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104659_W23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.5549</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104659_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-3.5125</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
